--- a/2026/ЗАВОДЫ/ПОКОМ/ОПТы/01,26/15,01,26 ПОКОМ КИ ПРС ЛП на погрузку с филиалами 19,01,26/Заказ ПРС 15,01,26.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/ОПТы/01,26/15,01,26 ПОКОМ КИ ПРС ЛП на погрузку с филиалами 19,01,26/Заказ ПРС 15,01,26.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\РАБОЧИЙ СТОЛ\15,01,26 ПОКОМ КИ ПРС ЛП на погрузку с филиалами 19,01,26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\2026\ЗАВОДЫ\ПОКОМ\ОПТы\01,26\15,01,26 ПОКОМ КИ ПРС ЛП на погрузку с филиалами 19,01,26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CE96FF-4939-4A11-BD14-062339C6B538}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24BCCF1B-EC8A-43FB-AF05-2DFCD3A0DB64}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -244,10 +244,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -986,7 +986,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -995,9 +995,9 @@
     </row>
     <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
-      <c r="B2" s="9"/>
+      <c r="B2" s="10"/>
       <c r="C2" s="3"/>
-      <c r="F2" s="10">
+      <c r="F2" s="9">
         <f>SUM(F4:F102)</f>
         <v>7323.25</v>
       </c>
@@ -1012,7 +1012,7 @@
       <c r="E3" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>36</v>
       </c>
     </row>
